--- a/dataset_t6_grouped/results2/G1/G1_T0374L_W0041F0001T0006Z000C1N4_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T0374L_W0041F0001T0006Z000C1N4_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>22.7964327833929</v>
+        <v>3.704420327301347</v>
       </c>
       <c r="D2" t="n">
-        <v>23.46409276333932</v>
+        <v>3.812915074042639</v>
       </c>
       <c r="E2" t="n">
-        <v>11.88956159824217</v>
+        <v>1.932053759714353</v>
       </c>
       <c r="F2" t="n">
-        <v>12.97235350519554</v>
+        <v>2.108007444594274</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>12.12949532154628</v>
+        <v>1.97104298975127</v>
       </c>
       <c r="D3" t="n">
-        <v>11.9283450825514</v>
+        <v>1.938356075914603</v>
       </c>
       <c r="E3" t="n">
-        <v>11.88956159824217</v>
+        <v>1.932053759714353</v>
       </c>
       <c r="F3" t="n">
-        <v>12.97235350519554</v>
+        <v>2.108007444594274</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>9.379922104840496</v>
+        <v>1.524237342036581</v>
       </c>
       <c r="D4" t="n">
-        <v>9.195464445725991</v>
+        <v>1.494262972430473</v>
       </c>
       <c r="E4" t="n">
-        <v>11.88956159824217</v>
+        <v>1.932053759714353</v>
       </c>
       <c r="F4" t="n">
-        <v>12.97235350519554</v>
+        <v>2.108007444594274</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>24.43897161299914</v>
+        <v>3.97133288711236</v>
       </c>
       <c r="D5" t="n">
-        <v>24.82257635624347</v>
+        <v>4.033668657889564</v>
       </c>
       <c r="E5" t="n">
-        <v>11.88956159824217</v>
+        <v>1.932053759714353</v>
       </c>
       <c r="F5" t="n">
-        <v>12.97235350519554</v>
+        <v>2.108007444594274</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>14.768773527741</v>
+        <v>2.399925698257912</v>
       </c>
       <c r="D6" t="n">
-        <v>33.9870349863162</v>
+        <v>5.522893185276383</v>
       </c>
       <c r="E6" t="n">
-        <v>11.88956159824217</v>
+        <v>1.932053759714353</v>
       </c>
       <c r="F6" t="n">
-        <v>12.97235350519554</v>
+        <v>2.108007444594274</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>5.590169943749475</v>
+        <v>0.9084026158592896</v>
       </c>
       <c r="D7" t="n">
-        <v>5.883957015711461</v>
+        <v>0.9561430150531125</v>
       </c>
       <c r="E7" t="n">
-        <v>11.88956159824217</v>
+        <v>1.932053759714353</v>
       </c>
       <c r="F7" t="n">
-        <v>12.97235350519554</v>
+        <v>2.108007444594274</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>23.18185897291734</v>
+        <v>3.767052083099067</v>
       </c>
       <c r="D8" t="n">
-        <v>37.99564608229627</v>
+        <v>6.174292488373144</v>
       </c>
       <c r="E8" t="n">
-        <v>11.88956159824217</v>
+        <v>1.932053759714353</v>
       </c>
       <c r="F8" t="n">
-        <v>12.97235350519554</v>
+        <v>2.108007444594274</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>29.3905241732502</v>
+        <v>4.775960178153158</v>
       </c>
       <c r="D9" t="n">
-        <v>29.91183931959355</v>
+        <v>4.860673889433952</v>
       </c>
       <c r="E9" t="n">
-        <v>11.88956159824217</v>
+        <v>1.932053759714353</v>
       </c>
       <c r="F9" t="n">
-        <v>12.97235350519554</v>
+        <v>2.108007444594274</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>14.1155942134931</v>
+        <v>2.29378405969263</v>
       </c>
       <c r="D10" t="n">
-        <v>13.55391829366323</v>
+        <v>2.202511722720275</v>
       </c>
       <c r="E10" t="n">
-        <v>11.88956159824217</v>
+        <v>1.932053759714353</v>
       </c>
       <c r="F10" t="n">
-        <v>12.97235350519554</v>
+        <v>2.108007444594274</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>33.59445935659447</v>
+        <v>5.459099645446601</v>
       </c>
       <c r="D11" t="n">
-        <v>34.2650226712361</v>
+        <v>5.568066184075867</v>
       </c>
       <c r="E11" t="n">
-        <v>11.88956159824217</v>
+        <v>1.932053759714353</v>
       </c>
       <c r="F11" t="n">
-        <v>12.97235350519554</v>
+        <v>2.108007444594274</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>38.59609077816994</v>
+        <v>6.271864751452615</v>
       </c>
       <c r="D12" t="n">
-        <v>39.54480010929433</v>
+        <v>6.426030017760328</v>
       </c>
       <c r="E12" t="n">
-        <v>11.88956159824217</v>
+        <v>1.932053759714353</v>
       </c>
       <c r="F12" t="n">
-        <v>12.97235350519554</v>
+        <v>2.108007444594274</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>10.6489299123967</v>
+        <v>1.730451110764465</v>
       </c>
       <c r="D13" t="n">
-        <v>8.469680017488033</v>
+        <v>1.376323002841805</v>
       </c>
       <c r="E13" t="n">
-        <v>11.88956159824217</v>
+        <v>1.932053759714353</v>
       </c>
       <c r="F13" t="n">
-        <v>12.97235350519554</v>
+        <v>2.108007444594274</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>20.90588402854856</v>
+        <v>3.397206154639142</v>
       </c>
       <c r="D14" t="n">
-        <v>8.30632453205142</v>
+        <v>1.349777736458356</v>
       </c>
       <c r="E14" t="n">
-        <v>11.88956159824217</v>
+        <v>1.932053759714353</v>
       </c>
       <c r="F14" t="n">
-        <v>12.97235350519554</v>
+        <v>2.108007444594274</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>40.84214207136731</v>
+        <v>6.636848086597189</v>
       </c>
       <c r="D15" t="n">
-        <v>41.81418500405115</v>
+        <v>6.794805063158312</v>
       </c>
       <c r="E15" t="n">
-        <v>11.88956159824217</v>
+        <v>1.932053759714353</v>
       </c>
       <c r="F15" t="n">
-        <v>12.97235350519554</v>
+        <v>2.108007444594274</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>18.94798207376276</v>
+        <v>3.079047086986449</v>
       </c>
       <c r="D16" t="n">
-        <v>18.86527124076565</v>
+        <v>3.065606576624419</v>
       </c>
       <c r="E16" t="n">
-        <v>11.88956159824217</v>
+        <v>1.932053759714353</v>
       </c>
       <c r="F16" t="n">
-        <v>12.97235350519554</v>
+        <v>2.108007444594274</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>19.78083062293305</v>
+        <v>3.214384976226621</v>
       </c>
       <c r="D17" t="n">
-        <v>20.99271465470769</v>
+        <v>3.41131613139</v>
       </c>
       <c r="E17" t="n">
-        <v>11.88956159824217</v>
+        <v>1.932053759714353</v>
       </c>
       <c r="F17" t="n">
-        <v>12.97235350519554</v>
+        <v>2.108007444594274</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>21.32344614564327</v>
+        <v>3.465059998667032</v>
       </c>
       <c r="D18" t="n">
-        <v>22.11912697911094</v>
+        <v>3.594358134105527</v>
       </c>
       <c r="E18" t="n">
-        <v>11.88956159824217</v>
+        <v>1.932053759714353</v>
       </c>
       <c r="F18" t="n">
-        <v>12.97235350519554</v>
+        <v>2.108007444594274</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>29.14980672833762</v>
+        <v>4.736843593354862</v>
       </c>
       <c r="D19" t="n">
-        <v>29.78041611127089</v>
+        <v>4.839317618081521</v>
       </c>
       <c r="E19" t="n">
-        <v>11.88956159824217</v>
+        <v>1.932053759714353</v>
       </c>
       <c r="F19" t="n">
-        <v>12.97235350519554</v>
+        <v>2.108007444594274</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>19.83746415130807</v>
+        <v>3.223587924587561</v>
       </c>
       <c r="D20" t="n">
-        <v>18.85857827913079</v>
+        <v>3.064518970358754</v>
       </c>
       <c r="E20" t="n">
-        <v>11.88956159824217</v>
+        <v>1.932053759714353</v>
       </c>
       <c r="F20" t="n">
-        <v>12.97235350519554</v>
+        <v>2.108007444594274</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>24.51292114807997</v>
+        <v>3.983349686562995</v>
       </c>
       <c r="D21" t="n">
-        <v>26.79244294434498</v>
+        <v>4.353771978456059</v>
       </c>
       <c r="E21" t="n">
-        <v>11.88956159824217</v>
+        <v>1.932053759714353</v>
       </c>
       <c r="F21" t="n">
-        <v>12.97235350519554</v>
+        <v>2.108007444594274</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>24.29869749287262</v>
+        <v>3.9485383425918</v>
       </c>
       <c r="D22" t="n">
-        <v>23.94848003164631</v>
+        <v>3.891628005142525</v>
       </c>
       <c r="E22" t="n">
-        <v>11.88956159824217</v>
+        <v>1.932053759714353</v>
       </c>
       <c r="F22" t="n">
-        <v>12.97235350519554</v>
+        <v>2.108007444594274</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>41.70737886633889</v>
+        <v>6.777449065780069</v>
       </c>
       <c r="D23" t="n">
-        <v>44.77263794552172</v>
+        <v>7.27555366614728</v>
       </c>
       <c r="E23" t="n">
-        <v>11.88956159824217</v>
+        <v>1.932053759714353</v>
       </c>
       <c r="F23" t="n">
-        <v>12.97235350519554</v>
+        <v>2.108007444594274</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1184,16 +1184,16 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>58.06170544647696</v>
+        <v>9.435027135052508</v>
       </c>
       <c r="D24" t="n">
-        <v>57.1405339042152</v>
+        <v>9.285336759434971</v>
       </c>
       <c r="E24" t="n">
-        <v>11.88956159824217</v>
+        <v>1.932053759714353</v>
       </c>
       <c r="F24" t="n">
-        <v>12.97235350519554</v>
+        <v>2.108007444594274</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
